--- a/Result/profitability/8076.xlsx
+++ b/Result/profitability/8076.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.22</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.001250000000000008</v>
+        <v>-0.03750000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>33.3</v>
+        <v>33.26625</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.86</v>
       </c>
       <c r="M3" t="n">
-        <v>0.04874999999999999</v>
+        <v>0.195</v>
       </c>
       <c r="N3" t="n">
-        <v>32.6225</v>
+        <v>32.85875</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>-0.8</v>
       </c>
       <c r="M4" t="n">
-        <v>0.07374999999999998</v>
+        <v>0.08999999999999998</v>
       </c>
       <c r="N4" t="n">
-        <v>32.74125</v>
+        <v>32.3</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.5600000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.001250000000000029</v>
+        <v>-0.01750000000000002</v>
       </c>
       <c r="N5" t="n">
-        <v>31.305</v>
+        <v>30.93625</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.15</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.05750000000000002</v>
+        <v>0.003749999999999986</v>
       </c>
       <c r="N6" t="n">
-        <v>30.0325</v>
+        <v>30.1675</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.62</v>
       </c>
       <c r="M7" t="n">
-        <v>0.05999999999999998</v>
+        <v>0.06499999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>29.705</v>
+        <v>29.675</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.06</v>
       </c>
       <c r="M8" t="n">
-        <v>0.05124999999999998</v>
+        <v>0.05249999999999998</v>
       </c>
       <c r="N8" t="n">
-        <v>29.345</v>
+        <v>29.00375</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1518,7 +1518,7 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0.03124999999999998</v>
+        <v>0.03124999999999999</v>
       </c>
       <c r="N9" t="n">
         <v>27.0425</v>
@@ -1645,7 +1645,7 @@
         <v>0.02</v>
       </c>
       <c r="M10" t="n">
-        <v>0.006249999999999976</v>
+        <v>0.006249999999999986</v>
       </c>
       <c r="N10" t="n">
         <v>26.41</v>
@@ -1901,7 +1901,7 @@
         <v>0.23</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.05250000000000002</v>
+        <v>-0.0525</v>
       </c>
       <c r="N12" t="n">
         <v>25.67375</v>
@@ -2028,7 +2028,7 @@
         <v>-0.6</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.05750000000000001</v>
+        <v>-0.0575</v>
       </c>
       <c r="N13" t="n">
         <v>25.3675</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>8076</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>697</v>
+      </c>
+      <c r="D75" t="n">
+        <v>472</v>
+      </c>
+      <c r="E75" t="n">
+        <v>225</v>
+      </c>
+      <c r="F75" t="n">
+        <v>32.29</v>
+      </c>
+      <c r="G75" t="n">
+        <v>65</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>9.30%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>2</v>
+      </c>
+      <c r="J75" t="n">
+        <v>67</v>
+      </c>
+      <c r="K75" t="n">
+        <v>49</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.007500000000000007</v>
+      </c>
+      <c r="N75" t="n">
+        <v>33.13375000000001</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.01000000000000001</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-2.730000000000004</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.0779554540262708</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.4333333333333332</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-2.950000000000003</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.08371169125993194</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
